--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.67928043472515</v>
+        <v>2.710383070642837</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01746239414161</v>
+        <v>2.765337639048012</v>
       </c>
       <c r="E2" t="n">
-        <v>12.73321455411841</v>
+        <v>2.069147365044242</v>
       </c>
       <c r="F2" t="n">
-        <v>5.229771054983456</v>
+        <v>0.8498377964348117</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.71346782556844</v>
+        <v>7.265938521654872</v>
       </c>
       <c r="D3" t="n">
-        <v>2.730769230769226</v>
+        <v>0.4437499999999993</v>
       </c>
       <c r="E3" t="n">
-        <v>12.73321455411841</v>
+        <v>2.069147365044242</v>
       </c>
       <c r="F3" t="n">
-        <v>5.229771054983456</v>
+        <v>0.8498377964348117</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.35197739585632</v>
+        <v>5.582196326826652</v>
       </c>
       <c r="D4" t="n">
-        <v>6.599562027511861</v>
+        <v>1.072428829470677</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73321455411841</v>
+        <v>2.069147365044242</v>
       </c>
       <c r="F4" t="n">
-        <v>5.229771054983456</v>
+        <v>0.8498377964348117</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.05040683095832</v>
+        <v>8.133191110030728</v>
       </c>
       <c r="D5" t="n">
-        <v>9.297382047330736</v>
+        <v>1.510824582691245</v>
       </c>
       <c r="E5" t="n">
-        <v>12.73321455411841</v>
+        <v>2.069147365044242</v>
       </c>
       <c r="F5" t="n">
-        <v>5.229771054983456</v>
+        <v>0.8498377964348117</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
